--- a/files/TMGH_Valuation_Study_15-06-2026_public.xlsx
+++ b/files/TMGH_Valuation_Study_15-06-2026_public.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Valuation" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Monte Carlo" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Sensitivity" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Calibration Ledger" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="464">
   <si>
     <t xml:space="preserve">READ FIRST — DISCLOSURE &amp; DISCLAIMER · TMGH VALUATION MODEL (EDUCATIONAL)</t>
   </si>
@@ -1283,6 +1284,147 @@
   </si>
   <si>
     <t xml:space="preserve">Price level →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALIBRATION LEDGER — universal, security-agnostic forecast record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every published forecast is logged here at its anchor and graded when the horizon matures. Schema is asset-class-agnostic (equity / metal / other) and identical across all studies. Grade-time columns stay blank until grade_date, then carry the realized outcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR (logged at publication)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREDICTED PERCENTILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOUCH BANDS — P(touch ±x% from anchor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRADE-TIME (blank until grade_date)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anchor price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ccy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-anchor from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P50 (median)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch +5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch +10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch +15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch +20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch −5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touch −10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realized close</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realized high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realized low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 90%?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 50%?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realized quantile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median err</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit +5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit +10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit +15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit +20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit −5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit −10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T+20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T+60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status is derived: a row is OPEN until realized_close is entered, then GRADED. in_90 / in_50 = realized_close within the P5–P95 / P25–P75 band. realized_quantile = empirical position of the realized close in the predicted distribution (0–1). median_err = realized_close − P50. Touch-hit flags record whether each ±x% level was reached within the horizon window.</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1450,7 @@
     <numFmt numFmtId="179" formatCode="#,##0.00"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1459,8 +1601,22 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF6B6B6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1497,8 +1653,14 @@
         <bgColor rgb="FFE6F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC98A2D"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1518,6 +1680,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFD4D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1547,7 +1718,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="104">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1928,6 +2099,42 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1953,7 +2160,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1B5E5E"/>
-      <rgbColor rgb="FFBFD4D4"/>
+      <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1962,7 +2169,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFBFD4D4"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1983,7 +2190,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFC98A2D"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF6B6B6B"/>
       <rgbColor rgb="FF969696"/>
@@ -4606,6 +4813,351 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AG9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="15" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="28" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="95" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="96" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="98" t="s">
+        <v>422</v>
+      </c>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+    </row>
+    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="99" t="s">
+        <v>423</v>
+      </c>
+      <c r="B5" s="99" t="s">
+        <v>424</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>425</v>
+      </c>
+      <c r="D5" s="99" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" s="99" t="s">
+        <v>427</v>
+      </c>
+      <c r="F5" s="99" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" s="99" t="s">
+        <v>428</v>
+      </c>
+      <c r="H5" s="99" t="s">
+        <v>429</v>
+      </c>
+      <c r="I5" s="99" t="s">
+        <v>430</v>
+      </c>
+      <c r="J5" s="99" t="s">
+        <v>431</v>
+      </c>
+      <c r="K5" s="99" t="s">
+        <v>432</v>
+      </c>
+      <c r="L5" s="99" t="s">
+        <v>433</v>
+      </c>
+      <c r="M5" s="99" t="s">
+        <v>434</v>
+      </c>
+      <c r="N5" s="99" t="s">
+        <v>435</v>
+      </c>
+      <c r="O5" s="99" t="s">
+        <v>436</v>
+      </c>
+      <c r="P5" s="99" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q5" s="99" t="s">
+        <v>438</v>
+      </c>
+      <c r="R5" s="99" t="s">
+        <v>439</v>
+      </c>
+      <c r="S5" s="99" t="s">
+        <v>440</v>
+      </c>
+      <c r="T5" s="99" t="s">
+        <v>441</v>
+      </c>
+      <c r="U5" s="99" t="s">
+        <v>442</v>
+      </c>
+      <c r="V5" s="99" t="s">
+        <v>443</v>
+      </c>
+      <c r="W5" s="99" t="s">
+        <v>444</v>
+      </c>
+      <c r="X5" s="99" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y5" s="99" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z5" s="99" t="s">
+        <v>447</v>
+      </c>
+      <c r="AA5" s="99" t="s">
+        <v>448</v>
+      </c>
+      <c r="AB5" s="99" t="s">
+        <v>449</v>
+      </c>
+      <c r="AC5" s="99" t="s">
+        <v>450</v>
+      </c>
+      <c r="AD5" s="99" t="s">
+        <v>451</v>
+      </c>
+      <c r="AE5" s="99" t="s">
+        <v>452</v>
+      </c>
+      <c r="AF5" s="99" t="s">
+        <v>453</v>
+      </c>
+      <c r="AG5" s="99" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="100" t="s">
+        <v>455</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>456</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>457</v>
+      </c>
+      <c r="D6" s="101" t="n">
+        <v>95.68</v>
+      </c>
+      <c r="E6" s="100" t="s">
+        <v>458</v>
+      </c>
+      <c r="F6" s="100" t="s">
+        <v>459</v>
+      </c>
+      <c r="G6" s="100" t="s">
+        <v>460</v>
+      </c>
+      <c r="H6" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="100" t="s">
+        <v>355</v>
+      </c>
+      <c r="J6" s="101" t="n">
+        <v>81.42</v>
+      </c>
+      <c r="K6" s="101" t="n">
+        <v>91.17</v>
+      </c>
+      <c r="L6" s="101" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="M6" s="101" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="N6" s="101" t="n">
+        <v>119.24</v>
+      </c>
+      <c r="O6" s="102" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P6" s="102" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q6" s="102" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R6" s="102" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S6" s="102" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T6" s="102" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="U6" s="100"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
+      <c r="X6" s="100"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="100"/>
+      <c r="AA6" s="100"/>
+      <c r="AB6" s="100"/>
+      <c r="AC6" s="100"/>
+      <c r="AD6" s="100"/>
+      <c r="AE6" s="100"/>
+      <c r="AF6" s="100"/>
+      <c r="AG6" s="100"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="100" t="s">
+        <v>455</v>
+      </c>
+      <c r="B7" s="100" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="100" t="s">
+        <v>457</v>
+      </c>
+      <c r="D7" s="101" t="n">
+        <v>95.68</v>
+      </c>
+      <c r="E7" s="100" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="100" t="s">
+        <v>461</v>
+      </c>
+      <c r="G7" s="100" t="s">
+        <v>462</v>
+      </c>
+      <c r="H7" s="100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="100" t="s">
+        <v>355</v>
+      </c>
+      <c r="J7" s="101" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="K7" s="101" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="L7" s="101" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="M7" s="101" t="n">
+        <v>118.41</v>
+      </c>
+      <c r="N7" s="101" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="O7" s="102" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P7" s="102" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q7" s="102" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R7" s="102" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S7" s="102" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T7" s="102" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="U7" s="100"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
+      <c r="X7" s="100"/>
+      <c r="Y7" s="100"/>
+      <c r="Z7" s="100"/>
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="100"/>
+      <c r="AD7" s="100"/>
+      <c r="AE7" s="100"/>
+      <c r="AF7" s="100"/>
+      <c r="AG7" s="100"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="103" t="s">
+        <v>463</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
